--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:33</t>
+    <t xml:space="preserve">2026-09-09 23:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -54,6 +54,9 @@
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santa Cruz</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:31</t>
+    <t xml:space="preserve">2026-09-17 14:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -676,13 +676,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6310</v>
+        <v>6204</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8.96</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="9">
@@ -693,13 +693,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6202</v>
+        <v>6310</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8.93</v>
+        <v>8.96</v>
       </c>
     </row>
     <row r="10">
@@ -710,13 +710,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6306</v>
+        <v>6202</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8.91</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="11">
@@ -727,13 +727,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6206</v>
+        <v>6306</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.84</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="12">
@@ -744,13 +744,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6302</v>
+        <v>6206</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8.69</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="13">
@@ -761,13 +761,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6305</v>
+        <v>6302</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8.36</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="14">
@@ -778,13 +778,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6112</v>
+        <v>6305</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8.29</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="15">
@@ -795,13 +795,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8.02</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="16">
@@ -812,13 +812,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6117</v>
+        <v>6109</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.96</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6307</v>
+        <v>6117</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.82</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7.58</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="19">
@@ -863,13 +863,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6114</v>
+        <v>6303</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7.4</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="20">
@@ -880,13 +880,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6116</v>
+        <v>6114</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7.18</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21">
@@ -897,13 +897,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7.14</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="22">
@@ -914,13 +914,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6309</v>
+        <v>6111</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6.85</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="23">
@@ -931,13 +931,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6103</v>
+        <v>6309</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6.66</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="24">
@@ -948,13 +948,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6301</v>
+        <v>6103</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6.64</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="25">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6205</v>
+        <v>6301</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>6.27</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6115</v>
+        <v>6205</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>6.11</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="27">
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6104</v>
+        <v>6115</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>5.88</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="28">
@@ -1016,13 +1016,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6110</v>
+        <v>6104</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5.73</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6102</v>
+        <v>6110</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>5.67</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6106</v>
+        <v>6102</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5.08</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6105</v>
+        <v>6106</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>4.94</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>4.63</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6108</v>
+        <v>6101</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3.34</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6108</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>3.34</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:25</t>
+    <t xml:space="preserve">2026-09-23 12:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:53</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1201,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-02 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:26</t>
+    <t xml:space="preserve">2026-10-02 15:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:16</t>
+    <t xml:space="preserve">2026-10-04 09:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:32</t>
+    <t xml:space="preserve">2026-10-05 12:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
